--- a/df_26.xlsx
+++ b/df_26.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M21"/>
+  <dimension ref="A1:M39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -518,7 +518,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Cruzeiro Saf</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -642,30 +642,30 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>20005</v>
+        <v>20007</v>
       </c>
       <c r="C5" t="n">
         <v>1</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Red Bull Bragantino</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Coritiba S.a.f.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -691,7 +691,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>20014</v>
+        <v>20385</v>
       </c>
       <c r="C6" t="n">
         <v>1</v>
@@ -703,7 +703,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -714,7 +714,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Vasco da Gama Saf</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -740,7 +740,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>20385</v>
+        <v>20005</v>
       </c>
       <c r="C7" t="n">
         <v>1</v>
@@ -752,7 +752,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -763,7 +763,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Vasco da Gama Saf</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -789,19 +789,19 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>61377</v>
+        <v>20014</v>
       </c>
       <c r="C8" t="n">
         <v>1</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -812,7 +812,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -838,7 +838,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>20052</v>
+        <v>61377</v>
       </c>
       <c r="C9" t="n">
         <v>1</v>
@@ -850,18 +850,18 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Athletico Paranaense</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -887,7 +887,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>20007</v>
+        <v>20052</v>
       </c>
       <c r="C10" t="n">
         <v>1</v>
@@ -899,7 +899,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Red Bull Bragantino</t>
+          <t>Athletico Paranaense</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -910,7 +910,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Coritiba S.a.f.</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -959,7 +959,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Atlético Mineiro Saf</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Atlético Mineiro Saf</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -1008,7 +1008,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1034,7 +1034,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>60646</v>
+        <v>20013</v>
       </c>
       <c r="C13" t="n">
         <v>1</v>
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Vasco da Gama Saf</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F13" t="n">
@@ -1057,7 +1057,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1083,30 +1083,30 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>20013</v>
+        <v>61590</v>
       </c>
       <c r="C14" t="n">
         <v>1</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Coritiba S.a.f.</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Red Bull Bragantino</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1132,19 +1132,19 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>20001</v>
+        <v>60646</v>
       </c>
       <c r="C15" t="n">
         <v>1</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Vasco da Gama Saf</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1279,7 +1279,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>61590</v>
+        <v>20001</v>
       </c>
       <c r="C18" t="n">
         <v>1</v>
@@ -1291,18 +1291,18 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Coritiba S.a.f.</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Red Bull Bragantino</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1438,7 +1438,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Cruzeiro Saf</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="F21" t="n">
@@ -1468,6 +1468,888 @@
       </c>
       <c r="M21" t="n">
         <v>20</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="B22" t="n">
+        <v>20007</v>
+      </c>
+      <c r="C22" t="n">
+        <v>2</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Red Bull Bragantino</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>1</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Atlético Mineiro</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="J22" t="n">
+        <v>6</v>
+      </c>
+      <c r="K22" t="n">
+        <v>2</v>
+      </c>
+      <c r="L22" t="n">
+        <v>2</v>
+      </c>
+      <c r="M22" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="B23" t="n">
+        <v>20002</v>
+      </c>
+      <c r="C23" t="n">
+        <v>2</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Palmeiras</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>5</v>
+      </c>
+      <c r="G23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="J23" t="n">
+        <v>4</v>
+      </c>
+      <c r="K23" t="n">
+        <v>1</v>
+      </c>
+      <c r="L23" t="n">
+        <v>4</v>
+      </c>
+      <c r="M23" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="B24" t="n">
+        <v>20086</v>
+      </c>
+      <c r="C24" t="n">
+        <v>2</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Chapecoense</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>1</v>
+      </c>
+      <c r="G24" t="n">
+        <v>1</v>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Vasco da Gama Saf</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="J24" t="n">
+        <v>4</v>
+      </c>
+      <c r="K24" t="n">
+        <v>1</v>
+      </c>
+      <c r="L24" t="n">
+        <v>2</v>
+      </c>
+      <c r="M24" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="B25" t="n">
+        <v>20385</v>
+      </c>
+      <c r="C25" t="n">
+        <v>2</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Mirassol</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>2</v>
+      </c>
+      <c r="G25" t="n">
+        <v>2</v>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Remo</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="J25" t="n">
+        <v>4</v>
+      </c>
+      <c r="K25" t="n">
+        <v>1</v>
+      </c>
+      <c r="L25" t="n">
+        <v>1</v>
+      </c>
+      <c r="M25" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="B26" t="n">
+        <v>20005</v>
+      </c>
+      <c r="C26" t="n">
+        <v>2</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>São Paulo</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>1</v>
+      </c>
+      <c r="G26" t="n">
+        <v>1</v>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Santos Fc</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="J26" t="n">
+        <v>4</v>
+      </c>
+      <c r="K26" t="n">
+        <v>1</v>
+      </c>
+      <c r="L26" t="n">
+        <v>1</v>
+      </c>
+      <c r="M26" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="B27" t="n">
+        <v>20014</v>
+      </c>
+      <c r="C27" t="n">
+        <v>2</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Fluminense</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>1</v>
+      </c>
+      <c r="G27" t="n">
+        <v>1</v>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Bahia</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="J27" t="n">
+        <v>4</v>
+      </c>
+      <c r="K27" t="n">
+        <v>1</v>
+      </c>
+      <c r="L27" t="n">
+        <v>1</v>
+      </c>
+      <c r="M27" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="B28" t="n">
+        <v>61377</v>
+      </c>
+      <c r="C28" t="n">
+        <v>2</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Bahia</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>1</v>
+      </c>
+      <c r="G28" t="n">
+        <v>1</v>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Fluminense</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="J28" t="n">
+        <v>4</v>
+      </c>
+      <c r="K28" t="n">
+        <v>1</v>
+      </c>
+      <c r="L28" t="n">
+        <v>1</v>
+      </c>
+      <c r="M28" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="B29" t="n">
+        <v>60175</v>
+      </c>
+      <c r="C29" t="n">
+        <v>2</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Botafogo</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>3</v>
+      </c>
+      <c r="G29" t="n">
+        <v>5</v>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Grêmio</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="J29" t="n">
+        <v>3</v>
+      </c>
+      <c r="K29" t="n">
+        <v>1</v>
+      </c>
+      <c r="L29" t="n">
+        <v>2</v>
+      </c>
+      <c r="M29" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n">
+        <v>28</v>
+      </c>
+      <c r="B30" t="n">
+        <v>20013</v>
+      </c>
+      <c r="C30" t="n">
+        <v>2</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Grêmio</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>5</v>
+      </c>
+      <c r="G30" t="n">
+        <v>3</v>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Botafogo</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="J30" t="n">
+        <v>3</v>
+      </c>
+      <c r="K30" t="n">
+        <v>1</v>
+      </c>
+      <c r="L30" t="n">
+        <v>1</v>
+      </c>
+      <c r="M30" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="n">
+        <v>61590</v>
+      </c>
+      <c r="C31" t="n">
+        <v>2</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Coritiba S.a.f.</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>2</v>
+      </c>
+      <c r="G31" t="n">
+        <v>1</v>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Cruzeiro</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="J31" t="n">
+        <v>3</v>
+      </c>
+      <c r="K31" t="n">
+        <v>1</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="n">
+        <v>20018</v>
+      </c>
+      <c r="C32" t="n">
+        <v>2</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>1</v>
+      </c>
+      <c r="G32" t="n">
+        <v>5</v>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Palmeiras</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="J32" t="n">
+        <v>3</v>
+      </c>
+      <c r="K32" t="n">
+        <v>1</v>
+      </c>
+      <c r="L32" t="n">
+        <v>-2</v>
+      </c>
+      <c r="M32" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="n">
+        <v>59849</v>
+      </c>
+      <c r="C33" t="n">
+        <v>2</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Coritiba S.a.f.</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>2</v>
+      </c>
+      <c r="G33" t="n">
+        <v>1</v>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Cruzeiro</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="J33" t="n">
+        <v>3</v>
+      </c>
+      <c r="K33" t="n">
+        <v>1</v>
+      </c>
+      <c r="L33" t="n">
+        <v>-3</v>
+      </c>
+      <c r="M33" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="n">
+        <v>60646</v>
+      </c>
+      <c r="C34" t="n">
+        <v>2</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Vasco da Gama Saf</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v>1</v>
+      </c>
+      <c r="G34" t="n">
+        <v>1</v>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Chapecoense</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="J34" t="n">
+        <v>1</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" t="n">
+        <v>-1</v>
+      </c>
+      <c r="M34" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="n">
+        <v>20016</v>
+      </c>
+      <c r="C35" t="n">
+        <v>2</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Flamengo</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
+        <v>1</v>
+      </c>
+      <c r="G35" t="n">
+        <v>1</v>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="J35" t="n">
+        <v>1</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" t="n">
+        <v>-1</v>
+      </c>
+      <c r="M35" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="n">
+        <v>62194</v>
+      </c>
+      <c r="C36" t="n">
+        <v>2</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Atlético Mineiro</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" t="n">
+        <v>1</v>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Red Bull Bragantino</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="J36" t="n">
+        <v>1</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" t="n">
+        <v>-1</v>
+      </c>
+      <c r="M36" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="n">
+        <v>20011</v>
+      </c>
+      <c r="C37" t="n">
+        <v>2</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+      <c r="F37" t="n">
+        <v>1</v>
+      </c>
+      <c r="G37" t="n">
+        <v>1</v>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Flamengo</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="J37" t="n">
+        <v>1</v>
+      </c>
+      <c r="K37" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" t="n">
+        <v>-1</v>
+      </c>
+      <c r="M37" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="n">
+        <v>20008</v>
+      </c>
+      <c r="C38" t="n">
+        <v>2</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Santos Fc</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
+        <v>1</v>
+      </c>
+      <c r="G38" t="n">
+        <v>1</v>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>São Paulo</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="J38" t="n">
+        <v>1</v>
+      </c>
+      <c r="K38" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" t="n">
+        <v>-2</v>
+      </c>
+      <c r="M38" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="n">
+        <v>20022</v>
+      </c>
+      <c r="C39" t="n">
+        <v>2</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Remo</t>
+        </is>
+      </c>
+      <c r="F39" t="n">
+        <v>2</v>
+      </c>
+      <c r="G39" t="n">
+        <v>2</v>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Mirassol</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="J39" t="n">
+        <v>1</v>
+      </c>
+      <c r="K39" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" t="n">
+        <v>-2</v>
+      </c>
+      <c r="M39" t="n">
+        <v>19</v>
       </c>
     </row>
   </sheetData>

--- a/df_26.xlsx
+++ b/df_26.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M39"/>
+  <dimension ref="A1:M59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -642,30 +642,30 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>20007</v>
+        <v>20005</v>
       </c>
       <c r="C5" t="n">
         <v>1</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Red Bull Bragantino</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Coritiba S.a.f.</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -691,7 +691,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>20385</v>
+        <v>20014</v>
       </c>
       <c r="C6" t="n">
         <v>1</v>
@@ -703,7 +703,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -714,7 +714,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Vasco da Gama Saf</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -740,19 +740,19 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>20005</v>
+        <v>61377</v>
       </c>
       <c r="C7" t="n">
         <v>1</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -763,7 +763,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -789,30 +789,30 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>20014</v>
+        <v>20052</v>
       </c>
       <c r="C8" t="n">
         <v>1</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Athletico Paranaense</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -838,7 +838,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>61377</v>
+        <v>20007</v>
       </c>
       <c r="C9" t="n">
         <v>1</v>
@@ -850,18 +850,18 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Red Bull Bragantino</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Coritiba S.a.f.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -887,30 +887,30 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>20052</v>
+        <v>20385</v>
       </c>
       <c r="C10" t="n">
         <v>1</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Athletico Paranaense</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Vasco da Gama Saf</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -992,23 +992,23 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
+          <t>Atlético Mineiro</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>2</v>
+      </c>
+      <c r="G12" t="n">
+        <v>2</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
           <t>Palmeiras</t>
-        </is>
-      </c>
-      <c r="F12" t="n">
-        <v>2</v>
-      </c>
-      <c r="G12" t="n">
-        <v>2</v>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1034,30 +1034,30 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>20013</v>
+        <v>61590</v>
       </c>
       <c r="C13" t="n">
         <v>1</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Coritiba S.a.f.</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Red Bull Bragantino</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1083,30 +1083,30 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>61590</v>
+        <v>20016</v>
       </c>
       <c r="C14" t="n">
         <v>1</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Coritiba S.a.f.</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Red Bull Bragantino</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1132,19 +1132,19 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>60646</v>
+        <v>20001</v>
       </c>
       <c r="C15" t="n">
         <v>1</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Vasco da Gama Saf</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1181,7 +1181,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>20016</v>
+        <v>20013</v>
       </c>
       <c r="C16" t="n">
         <v>1</v>
@@ -1193,7 +1193,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1230,30 +1230,30 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>20011</v>
+        <v>60646</v>
       </c>
       <c r="C17" t="n">
         <v>1</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Vasco da Gama Saf</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Athletico Paranaense</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1279,7 +1279,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>20001</v>
+        <v>20011</v>
       </c>
       <c r="C18" t="n">
         <v>1</v>
@@ -1291,18 +1291,18 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Athletico Paranaense</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1328,7 +1328,7 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>20008</v>
+        <v>20022</v>
       </c>
       <c r="C19" t="n">
         <v>1</v>
@@ -1340,18 +1340,18 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Santos Fc</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1377,7 +1377,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>20022</v>
+        <v>20008</v>
       </c>
       <c r="C20" t="n">
         <v>1</v>
@@ -1389,18 +1389,18 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Santos Fc</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G20" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1475,7 +1475,7 @@
         <v>20</v>
       </c>
       <c r="B22" t="n">
-        <v>20007</v>
+        <v>20052</v>
       </c>
       <c r="C22" t="n">
         <v>2</v>
@@ -1487,18 +1487,18 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Red Bull Bragantino</t>
+          <t>Athletico Paranaense</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Santos Fc</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1524,7 +1524,7 @@
         <v>21</v>
       </c>
       <c r="B23" t="n">
-        <v>20002</v>
+        <v>20007</v>
       </c>
       <c r="C23" t="n">
         <v>2</v>
@@ -1536,18 +1536,18 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Red Bull Bragantino</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1556,13 +1556,13 @@
         </is>
       </c>
       <c r="J23" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L23" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M23" t="n">
         <v>2</v>
@@ -1573,35 +1573,35 @@
         <v>22</v>
       </c>
       <c r="B24" t="n">
-        <v>20086</v>
+        <v>20002</v>
       </c>
       <c r="C24" t="n">
         <v>2</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G24" t="n">
         <v>1</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Vasco da Gama Saf</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>V</t>
         </is>
       </c>
       <c r="J24" t="n">
@@ -1611,7 +1611,7 @@
         <v>1</v>
       </c>
       <c r="L24" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M24" t="n">
         <v>3</v>
@@ -1622,7 +1622,7 @@
         <v>23</v>
       </c>
       <c r="B25" t="n">
-        <v>20385</v>
+        <v>20086</v>
       </c>
       <c r="C25" t="n">
         <v>2</v>
@@ -1634,18 +1634,18 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Vasco da Gama Saf</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1660,7 +1660,7 @@
         <v>1</v>
       </c>
       <c r="L25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M25" t="n">
         <v>4</v>
@@ -1818,7 +1818,7 @@
         <v>27</v>
       </c>
       <c r="B29" t="n">
-        <v>60175</v>
+        <v>20385</v>
       </c>
       <c r="C29" t="n">
         <v>2</v>
@@ -1830,33 +1830,33 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G29" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>E</t>
         </is>
       </c>
       <c r="J29" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K29" t="n">
         <v>1</v>
       </c>
       <c r="L29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M29" t="n">
         <v>8</v>
@@ -1867,35 +1867,35 @@
         <v>28</v>
       </c>
       <c r="B30" t="n">
-        <v>20013</v>
+        <v>60175</v>
       </c>
       <c r="C30" t="n">
         <v>2</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
+          <t>Botafogo</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>3</v>
+      </c>
+      <c r="G30" t="n">
+        <v>5</v>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
           <t>Grêmio</t>
         </is>
       </c>
-      <c r="F30" t="n">
-        <v>5</v>
-      </c>
-      <c r="G30" t="n">
-        <v>3</v>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Botafogo</t>
-        </is>
-      </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>D</t>
         </is>
       </c>
       <c r="J30" t="n">
@@ -1905,7 +1905,7 @@
         <v>1</v>
       </c>
       <c r="L30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M30" t="n">
         <v>9</v>
@@ -1913,33 +1913,33 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B31" t="n">
-        <v>61590</v>
+        <v>20001</v>
       </c>
       <c r="C31" t="n">
         <v>2</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Coritiba S.a.f.</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="F31" t="n">
         <v>2</v>
       </c>
       <c r="G31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Red Bull Bragantino</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -1954,46 +1954,46 @@
         <v>1</v>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M31" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B32" t="n">
-        <v>20018</v>
+        <v>20013</v>
       </c>
       <c r="C32" t="n">
         <v>2</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G32" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>V</t>
         </is>
       </c>
       <c r="J32" t="n">
@@ -2003,18 +2003,18 @@
         <v>1</v>
       </c>
       <c r="L32" t="n">
-        <v>-2</v>
+        <v>1</v>
       </c>
       <c r="M32" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B33" t="n">
-        <v>59849</v>
+        <v>61590</v>
       </c>
       <c r="C33" t="n">
         <v>2</v>
@@ -2052,64 +2052,64 @@
         <v>1</v>
       </c>
       <c r="L33" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B34" t="n">
-        <v>60646</v>
+        <v>20018</v>
       </c>
       <c r="C34" t="n">
         <v>2</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Vasco da Gama Saf</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="F34" t="n">
         <v>1</v>
       </c>
       <c r="G34" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="J34" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L34" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="M34" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B35" t="n">
         <v>20016</v>
@@ -2153,12 +2153,12 @@
         <v>-1</v>
       </c>
       <c r="M35" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B36" t="n">
         <v>62194</v>
@@ -2202,27 +2202,27 @@
         <v>-1</v>
       </c>
       <c r="M36" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B37" t="n">
-        <v>20011</v>
+        <v>60646</v>
       </c>
       <c r="C37" t="n">
         <v>2</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Vasco da Gama Saf</t>
         </is>
       </c>
       <c r="F37" t="n">
@@ -2233,7 +2233,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2251,27 +2251,27 @@
         <v>-1</v>
       </c>
       <c r="M37" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B38" t="n">
-        <v>20008</v>
+        <v>20011</v>
       </c>
       <c r="C38" t="n">
         <v>2</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Santos Fc</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="F38" t="n">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2297,15 +2297,15 @@
         <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="M38" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B39" t="n">
         <v>20022</v>
@@ -2349,7 +2349,987 @@
         <v>-2</v>
       </c>
       <c r="M39" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="n">
+        <v>38</v>
+      </c>
+      <c r="B40" t="n">
+        <v>20008</v>
+      </c>
+      <c r="C40" t="n">
+        <v>2</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Santos Fc</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
+        <v>1</v>
+      </c>
+      <c r="G40" t="n">
+        <v>1</v>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>São Paulo</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="J40" t="n">
+        <v>1</v>
+      </c>
+      <c r="K40" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" t="n">
+        <v>-2</v>
+      </c>
+      <c r="M40" t="n">
         <v>19</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="n">
+        <v>39</v>
+      </c>
+      <c r="B41" t="n">
+        <v>59849</v>
+      </c>
+      <c r="C41" t="n">
+        <v>2</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Cruzeiro</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
+        <v>1</v>
+      </c>
+      <c r="G41" t="n">
+        <v>2</v>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Coritiba S.a.f.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="J41" t="n">
+        <v>0</v>
+      </c>
+      <c r="K41" t="n">
+        <v>0</v>
+      </c>
+      <c r="L41" t="n">
+        <v>-5</v>
+      </c>
+      <c r="M41" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="n">
+        <v>40</v>
+      </c>
+      <c r="B42" t="n">
+        <v>20002</v>
+      </c>
+      <c r="C42" t="n">
+        <v>3</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Palmeiras</t>
+        </is>
+      </c>
+      <c r="F42" t="n">
+        <v>3</v>
+      </c>
+      <c r="G42" t="n">
+        <v>1</v>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="J42" t="n">
+        <v>7</v>
+      </c>
+      <c r="K42" t="n">
+        <v>2</v>
+      </c>
+      <c r="L42" t="n">
+        <v>6</v>
+      </c>
+      <c r="M42" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="n">
+        <v>41</v>
+      </c>
+      <c r="B43" t="n">
+        <v>20005</v>
+      </c>
+      <c r="C43" t="n">
+        <v>3</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>São Paulo</t>
+        </is>
+      </c>
+      <c r="F43" t="n">
+        <v>2</v>
+      </c>
+      <c r="G43" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Grêmio</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="J43" t="n">
+        <v>7</v>
+      </c>
+      <c r="K43" t="n">
+        <v>2</v>
+      </c>
+      <c r="L43" t="n">
+        <v>3</v>
+      </c>
+      <c r="M43" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="n">
+        <v>42</v>
+      </c>
+      <c r="B44" t="n">
+        <v>20014</v>
+      </c>
+      <c r="C44" t="n">
+        <v>3</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Fluminense</t>
+        </is>
+      </c>
+      <c r="F44" t="n">
+        <v>1</v>
+      </c>
+      <c r="G44" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Botafogo</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="J44" t="n">
+        <v>7</v>
+      </c>
+      <c r="K44" t="n">
+        <v>2</v>
+      </c>
+      <c r="L44" t="n">
+        <v>2</v>
+      </c>
+      <c r="M44" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="n">
+        <v>43</v>
+      </c>
+      <c r="B45" t="n">
+        <v>61377</v>
+      </c>
+      <c r="C45" t="n">
+        <v>3</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Bahia</t>
+        </is>
+      </c>
+      <c r="F45" t="n">
+        <v>1</v>
+      </c>
+      <c r="G45" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Vasco da Gama Saf</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="J45" t="n">
+        <v>7</v>
+      </c>
+      <c r="K45" t="n">
+        <v>2</v>
+      </c>
+      <c r="L45" t="n">
+        <v>2</v>
+      </c>
+      <c r="M45" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="n">
+        <v>20007</v>
+      </c>
+      <c r="C46" t="n">
+        <v>3</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Red Bull Bragantino</t>
+        </is>
+      </c>
+      <c r="F46" t="n">
+        <v>0</v>
+      </c>
+      <c r="G46" t="n">
+        <v>2</v>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Corinthians</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="J46" t="n">
+        <v>6</v>
+      </c>
+      <c r="K46" t="n">
+        <v>2</v>
+      </c>
+      <c r="L46" t="n">
+        <v>0</v>
+      </c>
+      <c r="M46" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="n">
+        <v>20086</v>
+      </c>
+      <c r="C47" t="n">
+        <v>3</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Chapecoense</t>
+        </is>
+      </c>
+      <c r="F47" t="n">
+        <v>3</v>
+      </c>
+      <c r="G47" t="n">
+        <v>3</v>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Coritiba S.a.f.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="J47" t="n">
+        <v>5</v>
+      </c>
+      <c r="K47" t="n">
+        <v>1</v>
+      </c>
+      <c r="L47" t="n">
+        <v>2</v>
+      </c>
+      <c r="M47" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="n">
+        <v>20385</v>
+      </c>
+      <c r="C48" t="n">
+        <v>3</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Mirassol</t>
+        </is>
+      </c>
+      <c r="F48" t="n">
+        <v>2</v>
+      </c>
+      <c r="G48" t="n">
+        <v>2</v>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Cruzeiro</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="J48" t="n">
+        <v>5</v>
+      </c>
+      <c r="K48" t="n">
+        <v>1</v>
+      </c>
+      <c r="L48" t="n">
+        <v>1</v>
+      </c>
+      <c r="M48" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="1" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" t="n">
+        <v>61590</v>
+      </c>
+      <c r="C49" t="n">
+        <v>3</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Coritiba S.a.f.</t>
+        </is>
+      </c>
+      <c r="F49" t="n">
+        <v>3</v>
+      </c>
+      <c r="G49" t="n">
+        <v>3</v>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Chapecoense</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="J49" t="n">
+        <v>4</v>
+      </c>
+      <c r="K49" t="n">
+        <v>1</v>
+      </c>
+      <c r="L49" t="n">
+        <v>0</v>
+      </c>
+      <c r="M49" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="1" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" t="n">
+        <v>20016</v>
+      </c>
+      <c r="C50" t="n">
+        <v>3</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Flamengo</t>
+        </is>
+      </c>
+      <c r="F50" t="n">
+        <v>2</v>
+      </c>
+      <c r="G50" t="n">
+        <v>1</v>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="J50" t="n">
+        <v>4</v>
+      </c>
+      <c r="K50" t="n">
+        <v>1</v>
+      </c>
+      <c r="L50" t="n">
+        <v>0</v>
+      </c>
+      <c r="M50" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" t="n">
+        <v>60175</v>
+      </c>
+      <c r="C51" t="n">
+        <v>3</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Botafogo</t>
+        </is>
+      </c>
+      <c r="F51" t="n">
+        <v>0</v>
+      </c>
+      <c r="G51" t="n">
+        <v>1</v>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Fluminense</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="J51" t="n">
+        <v>3</v>
+      </c>
+      <c r="K51" t="n">
+        <v>1</v>
+      </c>
+      <c r="L51" t="n">
+        <v>1</v>
+      </c>
+      <c r="M51" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="1" t="n">
+        <v>52</v>
+      </c>
+      <c r="B52" t="n">
+        <v>20013</v>
+      </c>
+      <c r="C52" t="n">
+        <v>3</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Grêmio</t>
+        </is>
+      </c>
+      <c r="F52" t="n">
+        <v>0</v>
+      </c>
+      <c r="G52" t="n">
+        <v>2</v>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>São Paulo</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="J52" t="n">
+        <v>3</v>
+      </c>
+      <c r="K52" t="n">
+        <v>1</v>
+      </c>
+      <c r="L52" t="n">
+        <v>-1</v>
+      </c>
+      <c r="M52" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="1" t="n">
+        <v>53</v>
+      </c>
+      <c r="B53" t="n">
+        <v>20018</v>
+      </c>
+      <c r="C53" t="n">
+        <v>3</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="F53" t="n">
+        <v>1</v>
+      </c>
+      <c r="G53" t="n">
+        <v>2</v>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Flamengo</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="J53" t="n">
+        <v>3</v>
+      </c>
+      <c r="K53" t="n">
+        <v>1</v>
+      </c>
+      <c r="L53" t="n">
+        <v>-3</v>
+      </c>
+      <c r="M53" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="1" t="n">
+        <v>54</v>
+      </c>
+      <c r="B54" t="n">
+        <v>62194</v>
+      </c>
+      <c r="C54" t="n">
+        <v>3</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Atlético Mineiro</t>
+        </is>
+      </c>
+      <c r="F54" t="n">
+        <v>3</v>
+      </c>
+      <c r="G54" t="n">
+        <v>3</v>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Remo</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="J54" t="n">
+        <v>2</v>
+      </c>
+      <c r="K54" t="n">
+        <v>0</v>
+      </c>
+      <c r="L54" t="n">
+        <v>-1</v>
+      </c>
+      <c r="M54" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="1" t="n">
+        <v>55</v>
+      </c>
+      <c r="B55" t="n">
+        <v>20022</v>
+      </c>
+      <c r="C55" t="n">
+        <v>3</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Remo</t>
+        </is>
+      </c>
+      <c r="F55" t="n">
+        <v>3</v>
+      </c>
+      <c r="G55" t="n">
+        <v>3</v>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Atlético Mineiro</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="J55" t="n">
+        <v>2</v>
+      </c>
+      <c r="K55" t="n">
+        <v>0</v>
+      </c>
+      <c r="L55" t="n">
+        <v>-2</v>
+      </c>
+      <c r="M55" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="1" t="n">
+        <v>56</v>
+      </c>
+      <c r="B56" t="n">
+        <v>60646</v>
+      </c>
+      <c r="C56" t="n">
+        <v>3</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Vasco da Gama Saf</t>
+        </is>
+      </c>
+      <c r="F56" t="n">
+        <v>0</v>
+      </c>
+      <c r="G56" t="n">
+        <v>1</v>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Bahia</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="J56" t="n">
+        <v>1</v>
+      </c>
+      <c r="K56" t="n">
+        <v>0</v>
+      </c>
+      <c r="L56" t="n">
+        <v>-2</v>
+      </c>
+      <c r="M56" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="1" t="n">
+        <v>57</v>
+      </c>
+      <c r="B57" t="n">
+        <v>20008</v>
+      </c>
+      <c r="C57" t="n">
+        <v>3</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Santos Fc</t>
+        </is>
+      </c>
+      <c r="F57" t="n">
+        <v>1</v>
+      </c>
+      <c r="G57" t="n">
+        <v>2</v>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Athletico Paranaense</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="J57" t="n">
+        <v>1</v>
+      </c>
+      <c r="K57" t="n">
+        <v>0</v>
+      </c>
+      <c r="L57" t="n">
+        <v>-3</v>
+      </c>
+      <c r="M57" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="1" t="n">
+        <v>58</v>
+      </c>
+      <c r="B58" t="n">
+        <v>20011</v>
+      </c>
+      <c r="C58" t="n">
+        <v>3</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+      <c r="F58" t="n">
+        <v>1</v>
+      </c>
+      <c r="G58" t="n">
+        <v>3</v>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Palmeiras</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="J58" t="n">
+        <v>1</v>
+      </c>
+      <c r="K58" t="n">
+        <v>0</v>
+      </c>
+      <c r="L58" t="n">
+        <v>-3</v>
+      </c>
+      <c r="M58" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="1" t="n">
+        <v>59</v>
+      </c>
+      <c r="B59" t="n">
+        <v>59849</v>
+      </c>
+      <c r="C59" t="n">
+        <v>3</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Cruzeiro</t>
+        </is>
+      </c>
+      <c r="F59" t="n">
+        <v>2</v>
+      </c>
+      <c r="G59" t="n">
+        <v>2</v>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Mirassol</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="J59" t="n">
+        <v>1</v>
+      </c>
+      <c r="K59" t="n">
+        <v>0</v>
+      </c>
+      <c r="L59" t="n">
+        <v>-5</v>
+      </c>
+      <c r="M59" t="n">
+        <v>20</v>
       </c>
     </row>
   </sheetData>
